--- a/ContractorLog.xlsx
+++ b/ContractorLog.xlsx
@@ -1,17 +1,24 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
-  <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="10328"/>
+  <workbookPr filterPrivacy="1"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="11_50252164007AE04D8663775BFDEE50B8D5149BD6" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <bookViews>
+    <workbookView xWindow="0" yWindow="660" windowWidth="34560" windowHeight="20120" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+  </bookViews>
   <sheets>
-    <sheet sheetId="1" name="ContractorLog" state="visible" r:id="rId4"/>
+    <sheet name="ContractorLog" sheetId="1" r:id="rId1"/>
+    <sheet name="EngineerOvertime" sheetId="2" r:id="rId2"/>
+    <sheet name="Managers" sheetId="3" r:id="rId3"/>
+    <sheet name="ContractorCompliance" sheetId="4" r:id="rId4"/>
   </sheets>
   <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="140" uniqueCount="84">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="284" uniqueCount="153">
   <si>
     <t>Date</t>
   </si>
@@ -58,201 +65,183 @@
     <t>2026-03-29</t>
   </si>
   <si>
-    <t>Pro-Door</t>
-  </si>
-  <si>
-    <t>john</t>
+    <t>CMBS</t>
+  </si>
+  <si>
+    <t>hays</t>
+  </si>
+  <si>
+    <t>002</t>
+  </si>
+  <si>
+    <t>House 15</t>
+  </si>
+  <si>
+    <t>Arbaaz Nawab</t>
+  </si>
+  <si>
+    <t>9889867667</t>
+  </si>
+  <si>
+    <t>No</t>
+  </si>
+  <si>
+    <t>Yes</t>
+  </si>
+  <si>
+    <t>2026-03-29 21:16:40</t>
+  </si>
+  <si>
+    <t>2026-03-29 22:19:32</t>
+  </si>
+  <si>
+    <t>hi</t>
+  </si>
+  <si>
+    <t>Completed</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>a</t>
+  </si>
+  <si>
+    <t>001</t>
+  </si>
+  <si>
+    <t>Laurel Anderson</t>
+  </si>
+  <si>
+    <t>9999999999</t>
+  </si>
+  <si>
+    <t>2026-03-29 22:07:07</t>
+  </si>
+  <si>
+    <t>2026-03-29 23:09:55</t>
+  </si>
+  <si>
+    <t>Trial</t>
+  </si>
+  <si>
+    <t>trail - AN</t>
+  </si>
+  <si>
+    <t>008</t>
+  </si>
+  <si>
+    <t>Goodenough Hotel, House 15</t>
+  </si>
+  <si>
+    <t>7946417786</t>
+  </si>
+  <si>
+    <t>2026-03-29 22:16:34</t>
+  </si>
+  <si>
+    <t>2026-03-29 23:10:07</t>
+  </si>
+  <si>
+    <t>Trial 21</t>
+  </si>
+  <si>
+    <t>Barrier</t>
+  </si>
+  <si>
+    <t>Aamir</t>
+  </si>
+  <si>
+    <t>999</t>
+  </si>
+  <si>
+    <t>Goodenough Hotel</t>
+  </si>
+  <si>
+    <t>9876543219</t>
+  </si>
+  <si>
+    <t>2026-03-29 22:17:07</t>
+  </si>
+  <si>
+    <t>2026-03-29 22:17:53</t>
+  </si>
+  <si>
+    <t>timepass</t>
+  </si>
+  <si>
+    <t>West End Decs</t>
+  </si>
+  <si>
+    <t>Sdgc</t>
+  </si>
+  <si>
+    <t>005</t>
+  </si>
+  <si>
+    <t>London House, Goodenough Hotel</t>
+  </si>
+  <si>
+    <t>Frankie Sheekey</t>
+  </si>
+  <si>
+    <t>9004461116</t>
+  </si>
+  <si>
+    <t>2026-03-29 23:20:06</t>
+  </si>
+  <si>
+    <t>2026-03-29 23:20:55</t>
+  </si>
+  <si>
+    <t>2026-03-30</t>
+  </si>
+  <si>
+    <t>Marshwell Firedoor</t>
+  </si>
+  <si>
+    <t>Trial 22</t>
+  </si>
+  <si>
+    <t>004</t>
+  </si>
+  <si>
+    <t>Goodenough Hotel, London House</t>
+  </si>
+  <si>
+    <t>9764521788</t>
+  </si>
+  <si>
+    <t>2026-03-30 11:30:37</t>
+  </si>
+  <si>
+    <t>2026-03-30 11:32:58</t>
+  </si>
+  <si>
+    <t>Changed boiler</t>
+  </si>
+  <si>
+    <t>Crest Lifts</t>
+  </si>
+  <si>
+    <t>Hdcb</t>
+  </si>
+  <si>
+    <t>2026-03-30 13:03:28</t>
+  </si>
+  <si>
+    <t>2026-03-30 18:31:45</t>
+  </si>
+  <si>
+    <t>change filters</t>
   </si>
   <si>
     <t>007</t>
   </si>
   <si>
-    <t>Goodenough Hotel</t>
-  </si>
-  <si>
     <t>Dean Marsh</t>
   </si>
   <si>
-    <t>10000000</t>
-  </si>
-  <si>
-    <t>Yes</t>
-  </si>
-  <si>
-    <t>2026-03-29 21:01:38</t>
-  </si>
-  <si>
-    <t>2026-03-29 21:05:37</t>
-  </si>
-  <si>
-    <t>Check the sheet</t>
-  </si>
-  <si>
-    <t>Completed</t>
-  </si>
-  <si>
-    <t/>
-  </si>
-  <si>
-    <t>CMBS</t>
-  </si>
-  <si>
-    <t>hays</t>
-  </si>
-  <si>
-    <t>002</t>
-  </si>
-  <si>
-    <t>House 15</t>
-  </si>
-  <si>
-    <t>Arbaaz Nawab</t>
-  </si>
-  <si>
-    <t>9889867667</t>
-  </si>
-  <si>
-    <t>No</t>
-  </si>
-  <si>
-    <t>2026-03-29 21:16:40</t>
-  </si>
-  <si>
-    <t>2026-03-29 22:19:32</t>
-  </si>
-  <si>
-    <t>hi</t>
-  </si>
-  <si>
-    <t>a</t>
-  </si>
-  <si>
-    <t>001</t>
-  </si>
-  <si>
-    <t>Laurel Anderson</t>
-  </si>
-  <si>
-    <t>9999999999</t>
-  </si>
-  <si>
-    <t>2026-03-29 22:07:07</t>
-  </si>
-  <si>
-    <t>2026-03-29 23:09:55</t>
-  </si>
-  <si>
-    <t>Trial</t>
-  </si>
-  <si>
-    <t>trail - AN</t>
-  </si>
-  <si>
-    <t>008</t>
-  </si>
-  <si>
-    <t>Goodenough Hotel, House 15</t>
-  </si>
-  <si>
-    <t>7946417786</t>
-  </si>
-  <si>
-    <t>2026-03-29 22:16:34</t>
-  </si>
-  <si>
-    <t>2026-03-29 23:10:07</t>
-  </si>
-  <si>
-    <t>Trial 21</t>
-  </si>
-  <si>
-    <t>Barrier</t>
-  </si>
-  <si>
-    <t>Aamir</t>
-  </si>
-  <si>
-    <t>999</t>
-  </si>
-  <si>
-    <t>9876543219</t>
-  </si>
-  <si>
-    <t>2026-03-29 22:17:07</t>
-  </si>
-  <si>
-    <t>2026-03-29 22:17:53</t>
-  </si>
-  <si>
-    <t>timepass</t>
-  </si>
-  <si>
-    <t>West End Decs</t>
-  </si>
-  <si>
-    <t>Sdgc</t>
-  </si>
-  <si>
-    <t>005</t>
-  </si>
-  <si>
-    <t>London House, Goodenough Hotel</t>
-  </si>
-  <si>
-    <t>Frankie Sheekey</t>
-  </si>
-  <si>
-    <t>9004461116</t>
-  </si>
-  <si>
-    <t>2026-03-29 23:20:06</t>
-  </si>
-  <si>
-    <t>2026-03-29 23:20:55</t>
-  </si>
-  <si>
-    <t>2026-03-30</t>
-  </si>
-  <si>
-    <t>Marshwell Firedoor</t>
-  </si>
-  <si>
-    <t>Trial 22</t>
-  </si>
-  <si>
-    <t>004</t>
-  </si>
-  <si>
-    <t>Goodenough Hotel, London House</t>
-  </si>
-  <si>
-    <t>9764521788</t>
-  </si>
-  <si>
-    <t>2026-03-30 11:30:37</t>
-  </si>
-  <si>
-    <t>2026-03-30 11:32:58</t>
-  </si>
-  <si>
-    <t>Changed boiler</t>
-  </si>
-  <si>
-    <t>Crest Lifts</t>
-  </si>
-  <si>
-    <t>Hdcb</t>
-  </si>
-  <si>
-    <t>2026-03-30 13:03:28</t>
-  </si>
-  <si>
-    <t>2026-03-30 18:31:45</t>
-  </si>
-  <si>
-    <t>change filters</t>
-  </si>
-  <si>
     <t>7771118094</t>
   </si>
   <si>
@@ -263,23 +252,251 @@
   </si>
   <si>
     <t>trial</t>
+  </si>
+  <si>
+    <t>CMM Buildings</t>
+  </si>
+  <si>
+    <t>Jaffer Nawab</t>
+  </si>
+  <si>
+    <t>9324110417</t>
+  </si>
+  <si>
+    <t>2026-03-30 19:41:26</t>
+  </si>
+  <si>
+    <t>2026-03-30 19:43:27</t>
+  </si>
+  <si>
+    <t>Vbnn</t>
+  </si>
+  <si>
+    <t>Interim Pest Control</t>
+  </si>
+  <si>
+    <t>Arbaaz Nawab BEng, MSc, MCIOB</t>
+  </si>
+  <si>
+    <t>2026-03-30 20:52:54</t>
+  </si>
+  <si>
+    <t>2026-03-30 20:55:11</t>
+  </si>
+  <si>
+    <t>Test</t>
+  </si>
+  <si>
+    <t>2026-03-31</t>
+  </si>
+  <si>
+    <t>alpha</t>
+  </si>
+  <si>
+    <t>003</t>
+  </si>
+  <si>
+    <t>2026-03-31 14:24:17</t>
+  </si>
+  <si>
+    <t>2026-03-31 14:26:44</t>
+  </si>
+  <si>
+    <t>2026-04-01</t>
+  </si>
+  <si>
+    <t>2026-04-01 16:21:53</t>
+  </si>
+  <si>
+    <t>2026-04-01 16:23:13</t>
+  </si>
+  <si>
+    <t>test</t>
+  </si>
+  <si>
+    <t>2026-04-05</t>
+  </si>
+  <si>
+    <t>Arbaaz</t>
+  </si>
+  <si>
+    <t>arbaaz</t>
+  </si>
+  <si>
+    <t>011</t>
+  </si>
+  <si>
+    <t>London House</t>
+  </si>
+  <si>
+    <t>07777777777</t>
+  </si>
+  <si>
+    <t>2026-04-05 22:41:35</t>
+  </si>
+  <si>
+    <t>Active</t>
+  </si>
+  <si>
+    <t>FIRST_TIME</t>
+  </si>
+  <si>
+    <t>Hot Works, Confined Space</t>
+  </si>
+  <si>
+    <t>Southern Commercial Kitchen</t>
+  </si>
+  <si>
+    <t>fg</t>
+  </si>
+  <si>
+    <t>777</t>
+  </si>
+  <si>
+    <t>1234567890</t>
+  </si>
+  <si>
+    <t>2026-04-05 23:00:17</t>
+  </si>
+  <si>
+    <t>Hot Works</t>
+  </si>
+  <si>
+    <t>Yes (Alarm isolation: No, Fire watch: No)</t>
+  </si>
+  <si>
+    <t>Engineer Name</t>
+  </si>
+  <si>
+    <t>Start Timestamp</t>
+  </si>
+  <si>
+    <t>End Timestamp</t>
+  </si>
+  <si>
+    <t>Work Description</t>
+  </si>
+  <si>
+    <t>Image Path</t>
+  </si>
+  <si>
+    <t>Approval Status</t>
+  </si>
+  <si>
+    <t>Approved By</t>
+  </si>
+  <si>
+    <t>Approval Timestamp</t>
+  </si>
+  <si>
+    <t>Notes</t>
+  </si>
+  <si>
+    <t>Donnel</t>
+  </si>
+  <si>
+    <t>2026-04-05 15:14:54</t>
+  </si>
+  <si>
+    <t>2026-04-05 16:39:55</t>
+  </si>
+  <si>
+    <t>I have changed the toilet bidet as the old version was leaking</t>
+  </si>
+  <si>
+    <t>COMPLETED</t>
+  </si>
+  <si>
+    <t>APPROVED</t>
+  </si>
+  <si>
+    <t>2026-04-05 16:40:53</t>
+  </si>
+  <si>
+    <t>Leakage in toilet level 2 LH</t>
+  </si>
+  <si>
+    <t>Lukasz</t>
+  </si>
+  <si>
+    <t>2026-04-05 22:44:29</t>
+  </si>
+  <si>
+    <t>ACTIVE</t>
+  </si>
+  <si>
+    <t>check the boiler</t>
+  </si>
+  <si>
+    <t>Manager Name</t>
+  </si>
+  <si>
+    <t>Manager Pin</t>
+  </si>
+  <si>
+    <t>RAMS Date</t>
+  </si>
+  <si>
+    <t>Induction Date</t>
+  </si>
+  <si>
+    <t>Insurance Date</t>
+  </si>
+  <si>
+    <t>RAMS Expiry</t>
+  </si>
+  <si>
+    <t>Induction Expiry</t>
+  </si>
+  <si>
+    <t>Insurance Expiry</t>
+  </si>
+  <si>
+    <t>Document Path</t>
+  </si>
+  <si>
+    <t>Updated By</t>
+  </si>
+  <si>
+    <t>Updated At</t>
+  </si>
+  <si>
+    <t>2026-04-02</t>
+  </si>
+  <si>
+    <t>2026-10-02</t>
+  </si>
+  <si>
+    <t>2027-04-02</t>
+  </si>
+  <si>
+    <t>/Users/896166/Library/CloudStorage/OneDrive-hull.ac.uk/Other/Arbaaz/contractor_attendance/Contractor Compliances/Arbaaz/1775427864646.pdf</t>
+  </si>
+  <si>
+    <t>Manager</t>
+  </si>
+  <si>
+    <t>2026-04-05 23:24:24</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="2" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
       <color theme="1"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
-      <sz val="11"/>
-      <name val="Calibri"/>
     </font>
     <font>
       <b/>
+      <sz val="11"/>
       <color rgb="FFFFFFFF"/>
+      <name val="Calibri"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="3">
@@ -648,9 +865,9 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:N10"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:Y15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="4" width="22" customWidth="1"/>
     <col min="5" max="5" width="45" customWidth="1"/>
@@ -662,7 +879,7 @@
     <col min="14" max="14" width="45" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="20" customHeight="1" spans="1:14" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:25" s="1" customFormat="1" ht="26.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -706,7 +923,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>14</v>
       </c>
@@ -732,30 +949,30 @@
         <v>21</v>
       </c>
       <c r="I2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="K2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="L2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="M2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="N2" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.25">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="3" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>14</v>
       </c>
       <c r="B3" t="s">
-        <v>27</v>
+        <v>15</v>
       </c>
       <c r="C3" t="s">
         <v>28</v>
@@ -764,195 +981,195 @@
         <v>29</v>
       </c>
       <c r="E3" t="s">
+        <v>18</v>
+      </c>
+      <c r="F3" t="s">
         <v>30</v>
       </c>
-      <c r="F3" t="s">
+      <c r="G3" t="s">
         <v>31</v>
       </c>
-      <c r="G3" t="s">
+      <c r="H3" t="s">
+        <v>22</v>
+      </c>
+      <c r="I3" t="s">
+        <v>22</v>
+      </c>
+      <c r="J3" t="s">
         <v>32</v>
       </c>
-      <c r="H3" t="s">
+      <c r="K3" t="s">
         <v>33</v>
       </c>
-      <c r="I3" t="s">
-        <v>21</v>
-      </c>
-      <c r="J3" t="s">
+      <c r="L3" t="s">
         <v>34</v>
       </c>
-      <c r="K3" t="s">
-        <v>35</v>
-      </c>
-      <c r="L3" t="s">
-        <v>36</v>
-      </c>
       <c r="M3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="N3" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.25">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="4" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>14</v>
       </c>
       <c r="B4" t="s">
-        <v>27</v>
+        <v>15</v>
       </c>
       <c r="C4" t="s">
+        <v>35</v>
+      </c>
+      <c r="D4" t="s">
+        <v>36</v>
+      </c>
+      <c r="E4" t="s">
         <v>37</v>
       </c>
-      <c r="D4" t="s">
+      <c r="F4" t="s">
+        <v>19</v>
+      </c>
+      <c r="G4" t="s">
         <v>38</v>
       </c>
-      <c r="E4" t="s">
-        <v>30</v>
-      </c>
-      <c r="F4" t="s">
+      <c r="H4" t="s">
+        <v>22</v>
+      </c>
+      <c r="I4" t="s">
+        <v>22</v>
+      </c>
+      <c r="J4" t="s">
         <v>39</v>
       </c>
-      <c r="G4" t="s">
+      <c r="K4" t="s">
         <v>40</v>
       </c>
-      <c r="H4" t="s">
-        <v>21</v>
-      </c>
-      <c r="I4" t="s">
-        <v>21</v>
-      </c>
-      <c r="J4" t="s">
+      <c r="L4" t="s">
         <v>41</v>
       </c>
-      <c r="K4" t="s">
-        <v>42</v>
-      </c>
-      <c r="L4" t="s">
-        <v>43</v>
-      </c>
       <c r="M4" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="N4" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.25">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="5" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>14</v>
       </c>
       <c r="B5" t="s">
-        <v>27</v>
+        <v>42</v>
       </c>
       <c r="C5" t="s">
+        <v>43</v>
+      </c>
+      <c r="D5" t="s">
         <v>44</v>
       </c>
-      <c r="D5" t="s">
+      <c r="E5" t="s">
         <v>45</v>
       </c>
-      <c r="E5" t="s">
+      <c r="F5" t="s">
+        <v>19</v>
+      </c>
+      <c r="G5" t="s">
         <v>46</v>
       </c>
-      <c r="F5" t="s">
-        <v>31</v>
-      </c>
-      <c r="G5" t="s">
+      <c r="H5" t="s">
+        <v>22</v>
+      </c>
+      <c r="I5" t="s">
+        <v>22</v>
+      </c>
+      <c r="J5" t="s">
         <v>47</v>
       </c>
-      <c r="H5" t="s">
-        <v>21</v>
-      </c>
-      <c r="I5" t="s">
-        <v>21</v>
-      </c>
-      <c r="J5" t="s">
+      <c r="K5" t="s">
         <v>48</v>
       </c>
-      <c r="K5" t="s">
+      <c r="L5" t="s">
         <v>49</v>
       </c>
-      <c r="L5" t="s">
-        <v>50</v>
-      </c>
       <c r="M5" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="N5" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.25">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="6" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>14</v>
       </c>
       <c r="B6" t="s">
+        <v>50</v>
+      </c>
+      <c r="C6" t="s">
         <v>51</v>
       </c>
-      <c r="C6" t="s">
+      <c r="D6" t="s">
         <v>52</v>
       </c>
-      <c r="D6" t="s">
+      <c r="E6" t="s">
         <v>53</v>
       </c>
-      <c r="E6" t="s">
-        <v>18</v>
-      </c>
       <c r="F6" t="s">
-        <v>31</v>
+        <v>54</v>
       </c>
       <c r="G6" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="H6" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I6" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J6" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="K6" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="L6" t="s">
-        <v>57</v>
+        <v>34</v>
       </c>
       <c r="M6" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="N6" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.25">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="7" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>14</v>
+        <v>58</v>
       </c>
       <c r="B7" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C7" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="D7" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E7" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="F7" t="s">
-        <v>62</v>
+        <v>19</v>
       </c>
       <c r="G7" t="s">
         <v>63</v>
       </c>
       <c r="H7" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I7" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J7" t="s">
         <v>64</v>
@@ -961,18 +1178,18 @@
         <v>65</v>
       </c>
       <c r="L7" t="s">
-        <v>43</v>
+        <v>66</v>
       </c>
       <c r="M7" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="N7" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.25">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="8" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>66</v>
+        <v>58</v>
       </c>
       <c r="B8" t="s">
         <v>67</v>
@@ -981,98 +1198,98 @@
         <v>68</v>
       </c>
       <c r="D8" t="s">
+        <v>36</v>
+      </c>
+      <c r="E8" t="s">
+        <v>62</v>
+      </c>
+      <c r="F8" t="s">
+        <v>30</v>
+      </c>
+      <c r="G8" t="s">
+        <v>55</v>
+      </c>
+      <c r="H8" t="s">
+        <v>22</v>
+      </c>
+      <c r="I8" t="s">
+        <v>22</v>
+      </c>
+      <c r="J8" t="s">
         <v>69</v>
       </c>
-      <c r="E8" t="s">
+      <c r="K8" t="s">
         <v>70</v>
       </c>
-      <c r="F8" t="s">
-        <v>31</v>
-      </c>
-      <c r="G8" t="s">
+      <c r="L8" t="s">
         <v>71</v>
       </c>
-      <c r="H8" t="s">
-        <v>21</v>
-      </c>
-      <c r="I8" t="s">
-        <v>21</v>
-      </c>
-      <c r="J8" t="s">
+      <c r="M8" t="s">
+        <v>26</v>
+      </c>
+      <c r="N8" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="9" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A9" t="s">
+        <v>58</v>
+      </c>
+      <c r="B9" t="s">
+        <v>59</v>
+      </c>
+      <c r="C9" t="s">
+        <v>19</v>
+      </c>
+      <c r="D9" t="s">
         <v>72</v>
       </c>
-      <c r="K8" t="s">
+      <c r="E9" t="s">
+        <v>62</v>
+      </c>
+      <c r="F9" t="s">
         <v>73</v>
       </c>
-      <c r="L8" t="s">
+      <c r="G9" t="s">
         <v>74</v>
       </c>
-      <c r="M8" t="s">
-        <v>25</v>
-      </c>
-      <c r="N8" t="s">
+      <c r="H9" t="s">
+        <v>22</v>
+      </c>
+      <c r="I9" t="s">
+        <v>22</v>
+      </c>
+      <c r="J9" t="s">
+        <v>75</v>
+      </c>
+      <c r="K9" t="s">
+        <v>76</v>
+      </c>
+      <c r="L9" t="s">
+        <v>77</v>
+      </c>
+      <c r="M9" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>66</v>
-      </c>
-      <c r="B9" t="s">
-        <v>75</v>
-      </c>
-      <c r="C9" t="s">
-        <v>76</v>
-      </c>
-      <c r="D9" t="s">
+      <c r="N9" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="10" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A10" t="s">
+        <v>58</v>
+      </c>
+      <c r="B10" t="s">
+        <v>78</v>
+      </c>
+      <c r="C10" t="s">
+        <v>79</v>
+      </c>
+      <c r="D10" t="s">
+        <v>52</v>
+      </c>
+      <c r="E10" t="s">
         <v>45</v>
-      </c>
-      <c r="E9" t="s">
-        <v>70</v>
-      </c>
-      <c r="F9" t="s">
-        <v>39</v>
-      </c>
-      <c r="G9" t="s">
-        <v>63</v>
-      </c>
-      <c r="H9" t="s">
-        <v>21</v>
-      </c>
-      <c r="I9" t="s">
-        <v>21</v>
-      </c>
-      <c r="J9" t="s">
-        <v>77</v>
-      </c>
-      <c r="K9" t="s">
-        <v>78</v>
-      </c>
-      <c r="L9" t="s">
-        <v>79</v>
-      </c>
-      <c r="M9" t="s">
-        <v>25</v>
-      </c>
-      <c r="N9" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
-        <v>66</v>
-      </c>
-      <c r="B10" t="s">
-        <v>67</v>
-      </c>
-      <c r="C10" t="s">
-        <v>31</v>
-      </c>
-      <c r="D10" t="s">
-        <v>17</v>
-      </c>
-      <c r="E10" t="s">
-        <v>70</v>
       </c>
       <c r="F10" t="s">
         <v>19</v>
@@ -1081,10 +1298,10 @@
         <v>80</v>
       </c>
       <c r="H10" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I10" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J10" t="s">
         <v>81</v>
@@ -1096,14 +1313,510 @@
         <v>83</v>
       </c>
       <c r="M10" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="N10" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="11" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A11" t="s">
+        <v>58</v>
+      </c>
+      <c r="B11" t="s">
+        <v>84</v>
+      </c>
+      <c r="C11" t="s">
+        <v>85</v>
+      </c>
+      <c r="D11" t="s">
+        <v>17</v>
+      </c>
+      <c r="E11" t="s">
+        <v>62</v>
+      </c>
+      <c r="F11" t="s">
+        <v>54</v>
+      </c>
+      <c r="G11" t="s">
+        <v>55</v>
+      </c>
+      <c r="H11" t="s">
+        <v>22</v>
+      </c>
+      <c r="I11" t="s">
+        <v>22</v>
+      </c>
+      <c r="J11" t="s">
+        <v>86</v>
+      </c>
+      <c r="K11" t="s">
+        <v>87</v>
+      </c>
+      <c r="L11" t="s">
+        <v>88</v>
+      </c>
+      <c r="M11" t="s">
         <v>26</v>
+      </c>
+      <c r="N11" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="12" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A12" t="s">
+        <v>89</v>
+      </c>
+      <c r="B12" t="s">
+        <v>67</v>
+      </c>
+      <c r="C12" t="s">
+        <v>90</v>
+      </c>
+      <c r="D12" t="s">
+        <v>91</v>
+      </c>
+      <c r="E12" t="s">
+        <v>45</v>
+      </c>
+      <c r="F12" t="s">
+        <v>30</v>
+      </c>
+      <c r="G12" t="s">
+        <v>74</v>
+      </c>
+      <c r="H12" t="s">
+        <v>22</v>
+      </c>
+      <c r="I12" t="s">
+        <v>22</v>
+      </c>
+      <c r="J12" t="s">
+        <v>92</v>
+      </c>
+      <c r="K12" t="s">
+        <v>93</v>
+      </c>
+      <c r="L12" t="s">
+        <v>77</v>
+      </c>
+      <c r="M12" t="s">
+        <v>26</v>
+      </c>
+      <c r="N12" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="13" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A13" t="s">
+        <v>94</v>
+      </c>
+      <c r="B13" t="s">
+        <v>42</v>
+      </c>
+      <c r="C13" t="s">
+        <v>90</v>
+      </c>
+      <c r="D13" t="s">
+        <v>72</v>
+      </c>
+      <c r="E13" t="s">
+        <v>45</v>
+      </c>
+      <c r="F13" t="s">
+        <v>19</v>
+      </c>
+      <c r="G13" t="s">
+        <v>74</v>
+      </c>
+      <c r="H13" t="s">
+        <v>22</v>
+      </c>
+      <c r="I13" t="s">
+        <v>22</v>
+      </c>
+      <c r="J13" t="s">
+        <v>95</v>
+      </c>
+      <c r="K13" t="s">
+        <v>96</v>
+      </c>
+      <c r="L13" t="s">
+        <v>97</v>
+      </c>
+      <c r="M13" t="s">
+        <v>26</v>
+      </c>
+      <c r="N13" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="14" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A14" t="s">
+        <v>98</v>
+      </c>
+      <c r="B14" t="s">
+        <v>99</v>
+      </c>
+      <c r="C14" t="s">
+        <v>100</v>
+      </c>
+      <c r="D14" t="s">
+        <v>101</v>
+      </c>
+      <c r="E14" t="s">
+        <v>102</v>
+      </c>
+      <c r="F14" t="s">
+        <v>19</v>
+      </c>
+      <c r="G14" t="s">
+        <v>103</v>
+      </c>
+      <c r="H14" t="s">
+        <v>22</v>
+      </c>
+      <c r="I14" t="s">
+        <v>22</v>
+      </c>
+      <c r="J14" t="s">
+        <v>104</v>
+      </c>
+      <c r="K14" t="s">
+        <v>27</v>
+      </c>
+      <c r="L14" t="s">
+        <v>27</v>
+      </c>
+      <c r="M14" t="s">
+        <v>105</v>
+      </c>
+      <c r="N14" t="s">
+        <v>27</v>
+      </c>
+      <c r="O14" t="s">
+        <v>106</v>
+      </c>
+      <c r="P14" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q14" t="s">
+        <v>107</v>
+      </c>
+      <c r="R14" t="s">
+        <v>21</v>
+      </c>
+      <c r="S14" t="s">
+        <v>22</v>
+      </c>
+      <c r="T14" t="s">
+        <v>22</v>
+      </c>
+      <c r="U14" t="s">
+        <v>21</v>
+      </c>
+      <c r="V14" t="s">
+        <v>22</v>
+      </c>
+      <c r="W14" t="s">
+        <v>98</v>
+      </c>
+      <c r="X14" t="s">
+        <v>27</v>
+      </c>
+      <c r="Y14" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="15" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A15" t="s">
+        <v>98</v>
+      </c>
+      <c r="B15" t="s">
+        <v>108</v>
+      </c>
+      <c r="C15" t="s">
+        <v>109</v>
+      </c>
+      <c r="D15" t="s">
+        <v>110</v>
+      </c>
+      <c r="E15" t="s">
+        <v>18</v>
+      </c>
+      <c r="F15" t="s">
+        <v>54</v>
+      </c>
+      <c r="G15" t="s">
+        <v>111</v>
+      </c>
+      <c r="H15" t="s">
+        <v>27</v>
+      </c>
+      <c r="I15" t="s">
+        <v>22</v>
+      </c>
+      <c r="J15" t="s">
+        <v>112</v>
+      </c>
+      <c r="K15" t="s">
+        <v>27</v>
+      </c>
+      <c r="L15" t="s">
+        <v>27</v>
+      </c>
+      <c r="M15" t="s">
+        <v>105</v>
+      </c>
+      <c r="N15" t="s">
+        <v>27</v>
+      </c>
+      <c r="O15" t="s">
+        <v>106</v>
+      </c>
+      <c r="P15" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q15" t="s">
+        <v>113</v>
+      </c>
+      <c r="R15" t="s">
+        <v>114</v>
+      </c>
+      <c r="S15" t="s">
+        <v>22</v>
+      </c>
+      <c r="T15" t="s">
+        <v>21</v>
+      </c>
+      <c r="U15" t="s">
+        <v>22</v>
+      </c>
+      <c r="V15" t="s">
+        <v>21</v>
+      </c>
+      <c r="W15" t="s">
+        <v>27</v>
+      </c>
+      <c r="X15" t="s">
+        <v>98</v>
+      </c>
+      <c r="Y15" t="s">
+        <v>27</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
+  <pageSetup orientation="portrait" useFirstPageNumber="1" horizontalDpi="4294967295" verticalDpi="4294967295"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+  <dimension ref="A1:J3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="10" width="30" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:10" s="1" customFormat="1" ht="26.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A2" t="s">
+        <v>124</v>
+      </c>
+      <c r="B2" t="s">
+        <v>125</v>
+      </c>
+      <c r="C2" t="s">
+        <v>126</v>
+      </c>
+      <c r="D2" t="s">
+        <v>127</v>
+      </c>
+      <c r="E2" t="s">
+        <v>27</v>
+      </c>
+      <c r="F2" t="s">
+        <v>128</v>
+      </c>
+      <c r="G2" t="s">
+        <v>129</v>
+      </c>
+      <c r="H2" t="s">
+        <v>19</v>
+      </c>
+      <c r="I2" t="s">
+        <v>130</v>
+      </c>
+      <c r="J2" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A3" t="s">
+        <v>132</v>
+      </c>
+      <c r="B3" t="s">
+        <v>133</v>
+      </c>
+      <c r="C3" t="s">
+        <v>27</v>
+      </c>
+      <c r="D3" t="s">
+        <v>27</v>
+      </c>
+      <c r="E3" t="s">
+        <v>27</v>
+      </c>
+      <c r="F3" t="s">
+        <v>134</v>
+      </c>
+      <c r="G3" t="s">
+        <v>27</v>
+      </c>
+      <c r="H3" t="s">
+        <v>27</v>
+      </c>
+      <c r="I3" t="s">
+        <v>27</v>
+      </c>
+      <c r="J3" t="s">
+        <v>135</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" useFirstPageNumber="1" horizontalDpi="4294967295" verticalDpi="4294967295"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+  <dimension ref="A1:B1"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="2" width="30" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" s="1" customFormat="1" ht="26.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>137</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" useFirstPageNumber="1" horizontalDpi="4294967295" verticalDpi="4294967295"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
+  <dimension ref="A1:J2"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="10" width="30" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:10" s="1" customFormat="1" ht="26.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A2" t="s">
+        <v>99</v>
+      </c>
+      <c r="B2" t="s">
+        <v>147</v>
+      </c>
+      <c r="C2" t="s">
+        <v>147</v>
+      </c>
+      <c r="D2" t="s">
+        <v>147</v>
+      </c>
+      <c r="E2" t="s">
+        <v>148</v>
+      </c>
+      <c r="F2" t="s">
+        <v>149</v>
+      </c>
+      <c r="G2" t="s">
+        <v>149</v>
+      </c>
+      <c r="H2" t="s">
+        <v>150</v>
+      </c>
+      <c r="I2" t="s">
+        <v>151</v>
+      </c>
+      <c r="J2" t="s">
+        <v>152</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" useFirstPageNumber="1" horizontalDpi="4294967295" verticalDpi="4294967295"/>
 </worksheet>
 </file>
--- a/ContractorLog.xlsx
+++ b/ContractorLog.xlsx
@@ -1,24 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="10328"/>
-  <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="11_50252164007AE04D8663775BFDEE50B8D5149BD6" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
+  <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="34560" windowHeight="20120" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="34560" windowHeight="20120" activeTab="3"/>
   </bookViews>
   <sheets>
-    <sheet name="ContractorLog" sheetId="1" r:id="rId1"/>
-    <sheet name="EngineerOvertime" sheetId="2" r:id="rId2"/>
-    <sheet name="Managers" sheetId="3" r:id="rId3"/>
-    <sheet name="ContractorCompliance" sheetId="4" r:id="rId4"/>
+    <sheet sheetId="1" name="ContractorLog" state="visible" r:id="rId4"/>
+    <sheet sheetId="2" name="EngineerOvertime" state="visible" r:id="rId5"/>
+    <sheet sheetId="3" name="Managers" state="visible" r:id="rId6"/>
+    <sheet sheetId="4" name="ContractorCompliance" state="visible" r:id="rId7"/>
   </sheets>
   <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="284" uniqueCount="153">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="285" uniqueCount="156">
   <si>
     <t>Date</t>
   </si>
@@ -422,10 +421,19 @@
     <t>2026-04-05 22:44:29</t>
   </si>
   <si>
-    <t>ACTIVE</t>
+    <t>2026-04-07 00:08:01</t>
+  </si>
+  <si>
+    <t>yes</t>
+  </si>
+  <si>
+    <t>2026-04-07 00:08:38</t>
   </si>
   <si>
     <t>check the boiler</t>
+  </si>
+  <si>
+    <t>2h 23m</t>
   </si>
   <si>
     <t>Manager Name</t>
@@ -482,21 +490,21 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <fonts count="2" x14ac:knownFonts="1">
     <font>
-      <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+      <sz val="11"/>
+      <name val="Calibri"/>
     </font>
     <font>
       <b/>
+      <color rgb="FFFFFFFF"/>
+      <family val="2"/>
       <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
       <name val="Calibri"/>
-      <family val="2"/>
     </font>
   </fonts>
   <fills count="3">
@@ -865,9 +873,9 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:Y15"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.2" defaultColWidth="8.83203125"/>
   <cols>
     <col min="1" max="4" width="22" customWidth="1"/>
     <col min="5" max="5" width="45" customWidth="1"/>
@@ -879,7 +887,7 @@
     <col min="14" max="14" width="45" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:25" s="1" customFormat="1" ht="26.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" ht="26.75" customHeight="1" spans="1:14" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -923,7 +931,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="2" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>14</v>
       </c>
@@ -967,7 +975,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="3" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>14</v>
       </c>
@@ -1011,7 +1019,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="4" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>14</v>
       </c>
@@ -1055,7 +1063,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="5" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>14</v>
       </c>
@@ -1099,7 +1107,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="6" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>14</v>
       </c>
@@ -1143,7 +1151,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="7" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>58</v>
       </c>
@@ -1187,7 +1195,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="8" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>58</v>
       </c>
@@ -1231,7 +1239,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="9" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>58</v>
       </c>
@@ -1275,7 +1283,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="10" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>58</v>
       </c>
@@ -1319,7 +1327,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="11" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>58</v>
       </c>
@@ -1363,7 +1371,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="12" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>89</v>
       </c>
@@ -1407,7 +1415,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="13" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>94</v>
       </c>
@@ -1451,7 +1459,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="14" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>98</v>
       </c>
@@ -1528,7 +1536,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="15" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>98</v>
       </c>
@@ -1607,19 +1615,19 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" useFirstPageNumber="1" horizontalDpi="4294967295" verticalDpi="4294967295"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:J3"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:K3"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.2" defaultColWidth="8.83203125"/>
   <cols>
     <col min="1" max="10" width="30" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" s="1" customFormat="1" ht="26.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" ht="26.75" customHeight="1" spans="1:10" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>115</v>
       </c>
@@ -1651,7 +1659,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>124</v>
       </c>
@@ -1683,7 +1691,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>132</v>
       </c>
@@ -1691,132 +1699,135 @@
         <v>133</v>
       </c>
       <c r="C3" t="s">
-        <v>27</v>
+        <v>134</v>
       </c>
       <c r="D3" t="s">
-        <v>27</v>
+        <v>135</v>
       </c>
       <c r="E3" t="s">
         <v>27</v>
       </c>
       <c r="F3" t="s">
-        <v>134</v>
+        <v>128</v>
       </c>
       <c r="G3" t="s">
-        <v>27</v>
+        <v>129</v>
       </c>
       <c r="H3" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="I3" t="s">
-        <v>27</v>
+        <v>136</v>
       </c>
       <c r="J3" t="s">
-        <v>135</v>
+        <v>137</v>
+      </c>
+      <c r="K3" t="s">
+        <v>138</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" useFirstPageNumber="1" horizontalDpi="4294967295" verticalDpi="4294967295"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:B1"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.2" defaultColWidth="8.83203125"/>
   <cols>
     <col min="1" max="2" width="30" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" s="1" customFormat="1" ht="26.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" ht="26.75" customHeight="1" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" useFirstPageNumber="1" horizontalDpi="4294967295" verticalDpi="4294967295"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:J2"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.2" defaultColWidth="8.83203125"/>
   <cols>
     <col min="1" max="10" width="30" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" s="1" customFormat="1" ht="26.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" ht="26.75" customHeight="1" spans="1:10" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>1</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.2">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>99</v>
       </c>
       <c r="B2" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="C2" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="D2" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="E2" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="F2" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="G2" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="H2" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="I2" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="J2" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" useFirstPageNumber="1" horizontalDpi="4294967295" verticalDpi="4294967295"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
 </worksheet>
 </file>